--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552801</v>
+        <v>124552803</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502728</v>
+        <v>502783</v>
       </c>
       <c r="R7" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552800</v>
+        <v>124552802</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502681</v>
+        <v>502708</v>
       </c>
       <c r="R8" t="n">
-        <v>6608117</v>
+        <v>6608189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552802</v>
+        <v>124552800</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502708</v>
+        <v>502681</v>
       </c>
       <c r="R9" t="n">
-        <v>6608189</v>
+        <v>6608117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552803</v>
+        <v>124552805</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502783</v>
+        <v>502786</v>
       </c>
       <c r="R10" t="n">
         <v>6608215</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552805</v>
+        <v>124552801</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502786</v>
+        <v>502728</v>
       </c>
       <c r="R11" t="n">
-        <v>6608215</v>
+        <v>6608163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552804</v>
+        <v>124552801</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502792</v>
+        <v>502728</v>
       </c>
       <c r="R6" t="n">
-        <v>6608220</v>
+        <v>6608163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552802</v>
+        <v>124552804</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502708</v>
+        <v>502792</v>
       </c>
       <c r="R8" t="n">
-        <v>6608189</v>
+        <v>6608220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552801</v>
+        <v>124552802</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502728</v>
+        <v>502708</v>
       </c>
       <c r="R11" t="n">
-        <v>6608163</v>
+        <v>6608189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552801</v>
+        <v>124552802</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502728</v>
+        <v>502708</v>
       </c>
       <c r="R6" t="n">
-        <v>6608163</v>
+        <v>6608189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552803</v>
+        <v>124552800</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502783</v>
+        <v>502681</v>
       </c>
       <c r="R7" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552800</v>
+        <v>124552803</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502681</v>
+        <v>502783</v>
       </c>
       <c r="R9" t="n">
-        <v>6608117</v>
+        <v>6608215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552802</v>
+        <v>124552801</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502708</v>
+        <v>502728</v>
       </c>
       <c r="R11" t="n">
-        <v>6608189</v>
+        <v>6608163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R6" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552800</v>
+        <v>124552804</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502681</v>
+        <v>502792</v>
       </c>
       <c r="R7" t="n">
-        <v>6608117</v>
+        <v>6608220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552804</v>
+        <v>124552802</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502792</v>
+        <v>502708</v>
       </c>
       <c r="R8" t="n">
-        <v>6608220</v>
+        <v>6608189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552803</v>
+        <v>124552801</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502783</v>
+        <v>502728</v>
       </c>
       <c r="R9" t="n">
-        <v>6608215</v>
+        <v>6608163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R10" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552801</v>
+        <v>124552803</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502728</v>
+        <v>502783</v>
       </c>
       <c r="R11" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R6" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552804</v>
+        <v>124552801</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502792</v>
+        <v>502728</v>
       </c>
       <c r="R7" t="n">
-        <v>6608220</v>
+        <v>6608163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R8" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552801</v>
+        <v>124552804</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502728</v>
+        <v>502792</v>
       </c>
       <c r="R9" t="n">
-        <v>6608163</v>
+        <v>6608220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552800</v>
+        <v>124552802</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502681</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6608117</v>
+        <v>6608189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552800</v>
+        <v>124552801</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502681</v>
+        <v>502728</v>
       </c>
       <c r="R6" t="n">
-        <v>6608117</v>
+        <v>6608163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552801</v>
+        <v>124552804</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502728</v>
+        <v>502792</v>
       </c>
       <c r="R7" t="n">
-        <v>6608163</v>
+        <v>6608220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552805</v>
+        <v>124552802</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502786</v>
+        <v>502708</v>
       </c>
       <c r="R8" t="n">
-        <v>6608215</v>
+        <v>6608189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552804</v>
+        <v>124552805</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502792</v>
+        <v>502786</v>
       </c>
       <c r="R9" t="n">
-        <v>6608220</v>
+        <v>6608215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552802</v>
+        <v>124552800</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502708</v>
+        <v>502681</v>
       </c>
       <c r="R10" t="n">
-        <v>6608189</v>
+        <v>6608117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552804</v>
+        <v>124552803</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502792</v>
+        <v>502783</v>
       </c>
       <c r="R7" t="n">
-        <v>6608220</v>
+        <v>6608215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552805</v>
+        <v>124552804</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502786</v>
+        <v>502792</v>
       </c>
       <c r="R9" t="n">
-        <v>6608215</v>
+        <v>6608220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552800</v>
+        <v>124552805</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502681</v>
+        <v>502786</v>
       </c>
       <c r="R10" t="n">
-        <v>6608117</v>
+        <v>6608215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552803</v>
+        <v>124552800</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502783</v>
+        <v>502681</v>
       </c>
       <c r="R11" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552801</v>
+        <v>124552802</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502728</v>
+        <v>502708</v>
       </c>
       <c r="R6" t="n">
-        <v>6608163</v>
+        <v>6608189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552803</v>
+        <v>124552805</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502783</v>
+        <v>502786</v>
       </c>
       <c r="R7" t="n">
         <v>6608215</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552802</v>
+        <v>124552801</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502708</v>
+        <v>502728</v>
       </c>
       <c r="R8" t="n">
-        <v>6608189</v>
+        <v>6608163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552805</v>
+        <v>124552803</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502786</v>
+        <v>502783</v>
       </c>
       <c r="R10" t="n">
         <v>6608215</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R6" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R7" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552801</v>
+        <v>124552804</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502728</v>
+        <v>502792</v>
       </c>
       <c r="R8" t="n">
-        <v>6608163</v>
+        <v>6608220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552804</v>
+        <v>124552803</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502792</v>
+        <v>502783</v>
       </c>
       <c r="R9" t="n">
-        <v>6608220</v>
+        <v>6608215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552803</v>
+        <v>124552801</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502783</v>
+        <v>502728</v>
       </c>
       <c r="R10" t="n">
-        <v>6608215</v>
+        <v>6608163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552800</v>
+        <v>124552802</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502681</v>
+        <v>502708</v>
       </c>
       <c r="R11" t="n">
-        <v>6608117</v>
+        <v>6608189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R6" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552800</v>
+        <v>124552804</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502681</v>
+        <v>502792</v>
       </c>
       <c r="R7" t="n">
-        <v>6608117</v>
+        <v>6608220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552804</v>
+        <v>124552805</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502792</v>
+        <v>502786</v>
       </c>
       <c r="R8" t="n">
-        <v>6608220</v>
+        <v>6608215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552801</v>
+        <v>124552802</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502728</v>
+        <v>502708</v>
       </c>
       <c r="R10" t="n">
-        <v>6608163</v>
+        <v>6608189</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552802</v>
+        <v>124552801</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502708</v>
+        <v>502728</v>
       </c>
       <c r="R11" t="n">
-        <v>6608189</v>
+        <v>6608163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552800</v>
+        <v>124552803</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502681</v>
+        <v>502783</v>
       </c>
       <c r="R6" t="n">
-        <v>6608117</v>
+        <v>6608215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552804</v>
+        <v>124552800</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502792</v>
+        <v>502681</v>
       </c>
       <c r="R7" t="n">
-        <v>6608220</v>
+        <v>6608117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552805</v>
+        <v>124552802</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502786</v>
+        <v>502708</v>
       </c>
       <c r="R8" t="n">
-        <v>6608215</v>
+        <v>6608189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552803</v>
+        <v>124552804</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502783</v>
+        <v>502792</v>
       </c>
       <c r="R9" t="n">
-        <v>6608215</v>
+        <v>6608220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R10" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552800</v>
+        <v>124552804</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502681</v>
+        <v>502792</v>
       </c>
       <c r="R7" t="n">
-        <v>6608117</v>
+        <v>6608220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552802</v>
+        <v>124552801</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502708</v>
+        <v>502728</v>
       </c>
       <c r="R8" t="n">
-        <v>6608189</v>
+        <v>6608163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552804</v>
+        <v>124552802</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502792</v>
+        <v>502708</v>
       </c>
       <c r="R9" t="n">
-        <v>6608220</v>
+        <v>6608189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R10" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552801</v>
+        <v>124552805</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502728</v>
+        <v>502786</v>
       </c>
       <c r="R11" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552803</v>
+        <v>124552801</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502783</v>
+        <v>502728</v>
       </c>
       <c r="R6" t="n">
-        <v>6608215</v>
+        <v>6608163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552801</v>
+        <v>124552803</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502728</v>
+        <v>502783</v>
       </c>
       <c r="R8" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R9" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552805</v>
+        <v>124552802</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502786</v>
+        <v>502708</v>
       </c>
       <c r="R11" t="n">
-        <v>6608215</v>
+        <v>6608189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552801</v>
+        <v>124552805</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502728</v>
+        <v>502786</v>
       </c>
       <c r="R6" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552803</v>
+        <v>124552801</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502783</v>
+        <v>502728</v>
       </c>
       <c r="R8" t="n">
-        <v>6608215</v>
+        <v>6608163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552805</v>
+        <v>124552800</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502786</v>
+        <v>502681</v>
       </c>
       <c r="R9" t="n">
-        <v>6608215</v>
+        <v>6608117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552800</v>
+        <v>124552803</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502681</v>
+        <v>502783</v>
       </c>
       <c r="R10" t="n">
-        <v>6608117</v>
+        <v>6608215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1267,7 +1267,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124552804</v>
+        <v>124552800</v>
       </c>
       <c r="B7" t="n">
         <v>105676</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502792</v>
+        <v>502681</v>
       </c>
       <c r="R7" t="n">
-        <v>6608220</v>
+        <v>6608117</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>0,5m höga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552801</v>
+        <v>124552802</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502728</v>
+        <v>502708</v>
       </c>
       <c r="R8" t="n">
-        <v>6608163</v>
+        <v>6608189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552800</v>
+        <v>124552804</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502681</v>
+        <v>502792</v>
       </c>
       <c r="R9" t="n">
-        <v>6608117</v>
+        <v>6608220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0,5m höga</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552802</v>
+        <v>124552801</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502708</v>
+        <v>502728</v>
       </c>
       <c r="R11" t="n">
-        <v>6608189</v>
+        <v>6608163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 8922-2020 artfynd.xlsx
+++ b/artfynd/A 8922-2020 artfynd.xlsx
@@ -1156,7 +1156,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124552805</v>
+        <v>124552802</v>
       </c>
       <c r="B6" t="n">
         <v>105676</v>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502786</v>
+        <v>502708</v>
       </c>
       <c r="R6" t="n">
-        <v>6608215</v>
+        <v>6608189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>2m höga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124552802</v>
+        <v>124552805</v>
       </c>
       <c r="B8" t="n">
         <v>105676</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502708</v>
+        <v>502786</v>
       </c>
       <c r="R8" t="n">
-        <v>6608189</v>
+        <v>6608215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124552804</v>
+        <v>124552801</v>
       </c>
       <c r="B9" t="n">
         <v>105676</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502792</v>
+        <v>502728</v>
       </c>
       <c r="R9" t="n">
-        <v>6608220</v>
+        <v>6608163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 m höga</t>
+          <t>1m höga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124552803</v>
+        <v>124552804</v>
       </c>
       <c r="B10" t="n">
         <v>105676</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502783</v>
+        <v>502792</v>
       </c>
       <c r="R10" t="n">
-        <v>6608215</v>
+        <v>6608220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
+          <t>1 m höga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124552801</v>
+        <v>124552803</v>
       </c>
       <c r="B11" t="n">
         <v>105676</v>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502728</v>
+        <v>502783</v>
       </c>
       <c r="R11" t="n">
-        <v>6608163</v>
+        <v>6608215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1m höga</t>
+          <t>12 m höga ca 15 cm dbh, askskottsjuka</t>
         </is>
       </c>
       <c r="AD11" t="b">
